--- a/sources/table_normalization/xlsx/economy-table98.xlsx
+++ b/sources/table_normalization/xlsx/economy-table98.xlsx
@@ -1179,13 +1179,6 @@
     <font>
       <i/>
       <sz val="9"/>
-      <color rgb="FF808080"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1210,8 +1203,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1232,6 +1231,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1468,9 +1473,6 @@
   </cellStyleXfs>
   <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -1479,9 +1481,6 @@
     </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -1516,32 +1515,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1559,6 +1540,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1867,7 +1872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1883,3585 +1888,3580 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="13" thickBot="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:59" ht="27" customHeight="1" thickBot="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24" t="s">
+      <c r="D2" s="29"/>
+      <c r="E2" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="25" t="s">
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="25"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="25"/>
-      <c r="AP2" s="25"/>
-      <c r="AQ2" s="25"/>
-      <c r="AR2" s="25"/>
-      <c r="AS2" s="25"/>
-      <c r="AT2" s="25"/>
-      <c r="AU2" s="25"/>
-      <c r="AV2" s="25"/>
-      <c r="AW2" s="25"/>
-      <c r="AX2" s="25"/>
-      <c r="AY2" s="25"/>
-      <c r="AZ2" s="25"/>
-      <c r="BA2" s="25"/>
-      <c r="BB2" s="25"/>
-      <c r="BC2" s="25"/>
-      <c r="BD2" s="25"/>
-      <c r="BE2" s="25"/>
-      <c r="BF2" s="25"/>
-      <c r="BG2" s="25"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="30"/>
+      <c r="AK2" s="30"/>
+      <c r="AL2" s="30"/>
+      <c r="AM2" s="30"/>
+      <c r="AN2" s="30"/>
+      <c r="AO2" s="30"/>
+      <c r="AP2" s="30"/>
+      <c r="AQ2" s="30"/>
+      <c r="AR2" s="30"/>
+      <c r="AS2" s="30"/>
+      <c r="AT2" s="30"/>
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="30"/>
+      <c r="AX2" s="30"/>
+      <c r="AY2" s="30"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="30"/>
+      <c r="BB2" s="30"/>
+      <c r="BC2" s="30"/>
+      <c r="BD2" s="30"/>
+      <c r="BE2" s="30"/>
+      <c r="BF2" s="30"/>
+      <c r="BG2" s="30"/>
     </row>
     <row r="3" spans="1:59" ht="44" customHeight="1" thickBot="1">
-      <c r="A3" s="26"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="27" t="s">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="I3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="27" t="s">
+      <c r="J3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="27" t="s">
+      <c r="N3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="28" t="s">
+      <c r="O3" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="27" t="s">
+      <c r="P3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="27" t="s">
+      <c r="Q3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="27" t="s">
+      <c r="R3" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="27" t="s">
+      <c r="S3" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="T3" s="27" t="s">
+      <c r="T3" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="U3" s="27" t="s">
+      <c r="U3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="V3" s="27" t="s">
+      <c r="V3" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="W3" s="27" t="s">
+      <c r="W3" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="X3" s="27" t="s">
+      <c r="X3" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="27" t="s">
+      <c r="Y3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="Z3" s="27" t="s">
+      <c r="Z3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="AA3" s="27" t="s">
+      <c r="AA3" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="AB3" s="27" t="s">
+      <c r="AB3" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="AC3" s="27" t="s">
+      <c r="AC3" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="AD3" s="27" t="s">
+      <c r="AD3" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AE3" s="27" t="s">
+      <c r="AE3" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="AF3" s="27" t="s">
+      <c r="AF3" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="AG3" s="27" t="s">
+      <c r="AG3" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="AH3" s="27" t="s">
+      <c r="AH3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="AI3" s="27" t="s">
+      <c r="AI3" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="AJ3" s="27" t="s">
+      <c r="AJ3" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="AK3" s="27" t="s">
+      <c r="AK3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="AL3" s="27" t="s">
+      <c r="AL3" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="AM3" s="27" t="s">
+      <c r="AM3" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="AN3" s="27" t="s">
+      <c r="AN3" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="AO3" s="27" t="s">
+      <c r="AO3" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="AP3" s="27" t="s">
+      <c r="AP3" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="AQ3" s="27" t="s">
+      <c r="AQ3" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="AR3" s="27" t="s">
+      <c r="AR3" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="AS3" s="27" t="s">
+      <c r="AS3" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AT3" s="27" t="s">
+      <c r="AT3" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="AU3" s="27" t="s">
+      <c r="AU3" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="AV3" s="27" t="s">
+      <c r="AV3" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="AW3" s="27" t="s">
+      <c r="AW3" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AX3" s="27" t="s">
+      <c r="AX3" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AY3" s="27" t="s">
+      <c r="AY3" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AZ3" s="27" t="s">
+      <c r="AZ3" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="BA3" s="27" t="s">
+      <c r="BA3" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="BB3" s="27" t="s">
+      <c r="BB3" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="BC3" s="27" t="s">
+      <c r="BC3" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="BD3" s="27" t="s">
+      <c r="BD3" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="BE3" s="27" t="s">
+      <c r="BE3" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="BF3" s="27" t="s">
+      <c r="BF3" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="BG3" s="29" t="s">
+      <c r="BG3" s="21" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:59" ht="27" customHeight="1">
-      <c r="A4" s="26"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="30" t="s">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="K4" s="30" t="s">
+      <c r="K4" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="L4" s="30" t="s">
+      <c r="L4" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="M4" s="30" t="s">
+      <c r="M4" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="N4" s="30" t="s">
+      <c r="N4" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="O4" s="31" t="s">
+      <c r="O4" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="P4" s="30" t="s">
+      <c r="P4" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="30" t="s">
+      <c r="Q4" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="R4" s="30" t="s">
+      <c r="R4" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="S4" s="30" t="s">
+      <c r="S4" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="T4" s="30" t="s">
+      <c r="T4" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="30" t="s">
+      <c r="U4" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="V4" s="30" t="s">
+      <c r="V4" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="W4" s="30" t="s">
+      <c r="W4" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="X4" s="30" t="s">
+      <c r="X4" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="Y4" s="30" t="s">
+      <c r="Y4" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="Z4" s="30" t="s">
+      <c r="Z4" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="AA4" s="30" t="s">
+      <c r="AA4" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="AB4" s="30" t="s">
+      <c r="AB4" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="AC4" s="30" t="s">
+      <c r="AC4" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="AD4" s="30" t="s">
+      <c r="AD4" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="AE4" s="30" t="s">
+      <c r="AE4" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="AF4" s="30" t="s">
+      <c r="AF4" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="AG4" s="30" t="s">
+      <c r="AG4" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="AH4" s="30" t="s">
+      <c r="AH4" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="AI4" s="30" t="s">
+      <c r="AI4" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="AJ4" s="30" t="s">
+      <c r="AJ4" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="AK4" s="30" t="s">
+      <c r="AK4" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="AL4" s="30" t="s">
+      <c r="AL4" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="AM4" s="30" t="s">
+      <c r="AM4" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="AN4" s="30" t="s">
+      <c r="AN4" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="AO4" s="30" t="s">
+      <c r="AO4" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="AP4" s="30" t="s">
+      <c r="AP4" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="AQ4" s="30" t="s">
+      <c r="AQ4" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="AR4" s="30" t="s">
+      <c r="AR4" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="AS4" s="30" t="s">
+      <c r="AS4" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="AT4" s="30" t="s">
+      <c r="AT4" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="AU4" s="30" t="s">
+      <c r="AU4" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="AV4" s="30" t="s">
+      <c r="AV4" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="AW4" s="30" t="s">
+      <c r="AW4" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="AX4" s="30" t="s">
+      <c r="AX4" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="AY4" s="30" t="s">
+      <c r="AY4" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="AZ4" s="30" t="s">
+      <c r="AZ4" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="BA4" s="30" t="s">
+      <c r="BA4" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="BB4" s="30" t="s">
+      <c r="BB4" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="BC4" s="30" t="s">
+      <c r="BC4" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="BD4" s="30" t="s">
+      <c r="BD4" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="BE4" s="30" t="s">
+      <c r="BE4" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="BF4" s="30" t="s">
+      <c r="BF4" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="BG4" s="32" t="s">
+      <c r="BG4" s="24" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>9388</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>3698</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>5690</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>1889</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>1563</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>844</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>2228</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>655</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>325</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <v>522</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>266</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <v>204</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <v>640</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" s="1">
         <v>252</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <v>426</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>821</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <v>222</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <v>83</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="2">
         <v>148</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="2">
         <v>224</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="2">
         <v>568</v>
       </c>
-      <c r="W5" s="3">
+      <c r="W5" s="2">
         <v>590</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="2">
         <v>181</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5" s="2">
         <v>51</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="Z5" s="2">
         <v>183</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="AA5" s="2">
         <v>201</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AB5" s="2">
         <v>415</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AC5" s="2">
         <v>275</v>
       </c>
-      <c r="AD5" s="3">
+      <c r="AD5" s="2">
         <v>1023</v>
       </c>
-      <c r="AE5" s="3">
+      <c r="AE5" s="2">
         <v>515</v>
       </c>
-      <c r="AF5" s="3">
+      <c r="AF5" s="2">
         <v>134</v>
       </c>
-      <c r="AG5" s="3">
+      <c r="AG5" s="2">
         <v>521</v>
       </c>
-      <c r="AH5" s="3">
+      <c r="AH5" s="2">
         <v>68</v>
       </c>
-      <c r="AI5" s="3">
+      <c r="AI5" s="2">
         <v>87</v>
       </c>
-      <c r="AJ5" s="3">
+      <c r="AJ5" s="2">
         <v>148</v>
       </c>
-      <c r="AK5" s="3">
+      <c r="AK5" s="2">
         <v>22</v>
       </c>
-      <c r="AL5" s="3">
+      <c r="AL5" s="2">
         <v>222</v>
       </c>
-      <c r="AM5" s="3">
+      <c r="AM5" s="2">
         <v>71</v>
       </c>
-      <c r="AN5" s="3">
+      <c r="AN5" s="2">
         <v>229</v>
       </c>
-      <c r="AO5" s="3">
+      <c r="AO5" s="2">
         <v>79</v>
       </c>
-      <c r="AP5" s="3">
+      <c r="AP5" s="2">
         <v>23</v>
       </c>
-      <c r="AQ5" s="3">
+      <c r="AQ5" s="2">
         <v>15</v>
       </c>
-      <c r="AR5" s="3">
+      <c r="AR5" s="2">
         <v>126</v>
       </c>
-      <c r="AS5" s="3">
+      <c r="AS5" s="2">
         <v>125</v>
       </c>
-      <c r="AT5" s="3">
+      <c r="AT5" s="2">
         <v>409</v>
       </c>
-      <c r="AU5" s="3">
+      <c r="AU5" s="2">
         <v>105</v>
       </c>
-      <c r="AV5" s="3">
+      <c r="AV5" s="2">
         <v>134</v>
       </c>
-      <c r="AW5" s="3">
+      <c r="AW5" s="2">
         <v>21</v>
       </c>
-      <c r="AX5" s="3">
+      <c r="AX5" s="2">
         <v>43</v>
       </c>
-      <c r="AY5" s="3">
+      <c r="AY5" s="2">
         <v>35</v>
       </c>
-      <c r="AZ5" s="3">
+      <c r="AZ5" s="2">
         <v>137</v>
       </c>
-      <c r="BA5" s="3">
+      <c r="BA5" s="2">
         <v>55</v>
       </c>
-      <c r="BB5" s="3">
+      <c r="BB5" s="2">
         <v>180</v>
       </c>
-      <c r="BC5" s="3">
+      <c r="BC5" s="2">
         <v>116</v>
       </c>
-      <c r="BD5" s="3">
+      <c r="BD5" s="2">
         <v>190</v>
       </c>
-      <c r="BE5" s="3">
+      <c r="BE5" s="2">
         <v>110</v>
       </c>
-      <c r="BF5" s="3">
+      <c r="BF5" s="2">
         <v>44</v>
       </c>
-      <c r="BG5" s="4">
+      <c r="BG5" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>27838</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>13275</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>14563</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>9047</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>3678</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>2217</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="5">
         <v>5222</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="5">
         <v>1719</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="5">
         <v>932</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="5">
         <v>1089</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="5">
         <v>915</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="5">
         <v>515</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="5">
         <v>1835</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="4">
         <v>669</v>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="5">
         <v>2541</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="Q6" s="5">
         <v>3896</v>
       </c>
-      <c r="R6" s="7">
+      <c r="R6" s="5">
         <v>515</v>
       </c>
-      <c r="S6" s="7">
+      <c r="S6" s="5">
         <v>309</v>
       </c>
-      <c r="T6" s="7">
+      <c r="T6" s="5">
         <v>1167</v>
       </c>
-      <c r="U6" s="7">
+      <c r="U6" s="5">
         <v>413</v>
       </c>
-      <c r="V6" s="7">
+      <c r="V6" s="5">
         <v>1206</v>
       </c>
-      <c r="W6" s="7">
+      <c r="W6" s="5">
         <v>1504</v>
       </c>
-      <c r="X6" s="7">
+      <c r="X6" s="5">
         <v>555</v>
       </c>
-      <c r="Y6" s="7">
+      <c r="Y6" s="5">
         <v>83</v>
       </c>
-      <c r="Z6" s="7">
+      <c r="Z6" s="5">
         <v>428</v>
       </c>
-      <c r="AA6" s="7">
+      <c r="AA6" s="5">
         <v>659</v>
       </c>
-      <c r="AB6" s="7">
+      <c r="AB6" s="5">
         <v>1205</v>
       </c>
-      <c r="AC6" s="7">
+      <c r="AC6" s="5">
         <v>540</v>
       </c>
-      <c r="AD6" s="7">
+      <c r="AD6" s="5">
         <v>2357</v>
       </c>
-      <c r="AE6" s="7">
+      <c r="AE6" s="5">
         <v>1121</v>
       </c>
-      <c r="AF6" s="7">
+      <c r="AF6" s="5">
         <v>339</v>
       </c>
-      <c r="AG6" s="7">
+      <c r="AG6" s="5">
         <v>1380</v>
       </c>
-      <c r="AH6" s="7">
+      <c r="AH6" s="5">
         <v>175</v>
       </c>
-      <c r="AI6" s="7">
+      <c r="AI6" s="5">
         <v>403</v>
       </c>
-      <c r="AJ6" s="7">
+      <c r="AJ6" s="5">
         <v>295</v>
       </c>
-      <c r="AK6" s="7">
+      <c r="AK6" s="5">
         <v>60</v>
       </c>
-      <c r="AL6" s="7">
+      <c r="AL6" s="5">
         <v>463</v>
       </c>
-      <c r="AM6" s="7">
+      <c r="AM6" s="5">
         <v>198</v>
       </c>
-      <c r="AN6" s="7">
+      <c r="AN6" s="5">
         <v>428</v>
       </c>
-      <c r="AO6" s="7">
+      <c r="AO6" s="5">
         <v>164</v>
       </c>
-      <c r="AP6" s="7">
+      <c r="AP6" s="5">
         <v>29</v>
       </c>
-      <c r="AQ6" s="7">
+      <c r="AQ6" s="5">
         <v>26</v>
       </c>
-      <c r="AR6" s="7">
+      <c r="AR6" s="5">
         <v>622</v>
       </c>
-      <c r="AS6" s="7">
+      <c r="AS6" s="5">
         <v>268</v>
       </c>
-      <c r="AT6" s="7">
+      <c r="AT6" s="5">
         <v>1048</v>
       </c>
-      <c r="AU6" s="7">
+      <c r="AU6" s="5">
         <v>217</v>
       </c>
-      <c r="AV6" s="7">
+      <c r="AV6" s="5">
         <v>430</v>
       </c>
-      <c r="AW6" s="7">
+      <c r="AW6" s="5">
         <v>59</v>
       </c>
-      <c r="AX6" s="7">
+      <c r="AX6" s="5">
         <v>105</v>
       </c>
-      <c r="AY6" s="7">
+      <c r="AY6" s="5">
         <v>134</v>
       </c>
-      <c r="AZ6" s="7">
+      <c r="AZ6" s="5">
         <v>450</v>
       </c>
-      <c r="BA6" s="7">
+      <c r="BA6" s="5">
         <v>189</v>
       </c>
-      <c r="BB6" s="7">
+      <c r="BB6" s="5">
         <v>367</v>
       </c>
-      <c r="BC6" s="7">
+      <c r="BC6" s="5">
         <v>279</v>
       </c>
-      <c r="BD6" s="7">
+      <c r="BD6" s="5">
         <v>837</v>
       </c>
-      <c r="BE6" s="7">
+      <c r="BE6" s="5">
         <v>226</v>
       </c>
-      <c r="BF6" s="7">
+      <c r="BF6" s="5">
         <v>126</v>
       </c>
-      <c r="BG6" s="8">
+      <c r="BG6" s="6">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>0.36</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="8">
         <v>0.4</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <v>0.31</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="8">
         <v>0.44</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="8">
         <v>0.35</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="8">
         <v>0.1</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="8">
         <v>0.36</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="8">
         <v>0.35</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="8">
         <v>0.17</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="8">
         <v>0.31</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="8">
         <v>0.42</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="8">
         <v>0.24</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="8">
         <v>0.38</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="7">
         <v>0.26</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="8">
         <v>0.39</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="Q7" s="8">
         <v>0.62</v>
       </c>
-      <c r="R7" s="10">
+      <c r="R7" s="8">
         <v>0.34</v>
       </c>
-      <c r="S7" s="10">
+      <c r="S7" s="8">
         <v>0.13</v>
       </c>
-      <c r="T7" s="10">
+      <c r="T7" s="8">
         <v>0.23</v>
       </c>
-      <c r="U7" s="10">
+      <c r="U7" s="8">
         <v>0.05</v>
       </c>
-      <c r="V7" s="10">
+      <c r="V7" s="8">
         <v>0.39</v>
       </c>
-      <c r="W7" s="10">
+      <c r="W7" s="8">
         <v>0.38</v>
       </c>
-      <c r="X7" s="10">
+      <c r="X7" s="8">
         <v>0.41</v>
       </c>
-      <c r="Y7" s="10">
+      <c r="Y7" s="8">
         <v>0.19</v>
       </c>
-      <c r="Z7" s="10">
+      <c r="Z7" s="8">
         <v>0.09</v>
       </c>
-      <c r="AA7" s="10">
+      <c r="AA7" s="8">
         <v>0.17</v>
       </c>
-      <c r="AB7" s="10">
+      <c r="AB7" s="8">
         <v>0.31</v>
       </c>
-      <c r="AC7" s="10">
+      <c r="AC7" s="8">
         <v>0.3</v>
       </c>
-      <c r="AD7" s="10">
+      <c r="AD7" s="8">
         <v>0.39</v>
       </c>
-      <c r="AE7" s="10">
+      <c r="AE7" s="8">
         <v>0.38</v>
       </c>
-      <c r="AF7" s="10">
+      <c r="AF7" s="8">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AG7" s="10">
+      <c r="AG7" s="8">
         <v>0.4</v>
       </c>
-      <c r="AH7" s="10">
+      <c r="AH7" s="8">
         <v>0.12</v>
       </c>
-      <c r="AI7" s="10">
+      <c r="AI7" s="8">
         <v>0.15</v>
       </c>
-      <c r="AJ7" s="10">
+      <c r="AJ7" s="8">
         <v>0.22</v>
       </c>
-      <c r="AK7" s="3"/>
-      <c r="AL7" s="10">
+      <c r="AK7" s="2"/>
+      <c r="AL7" s="8">
         <v>0.39</v>
       </c>
-      <c r="AM7" s="10">
+      <c r="AM7" s="8">
         <v>0.22</v>
       </c>
-      <c r="AN7" s="10">
+      <c r="AN7" s="8">
         <v>0.27</v>
       </c>
-      <c r="AO7" s="10">
+      <c r="AO7" s="8">
         <v>0.17</v>
       </c>
-      <c r="AP7" s="3"/>
-      <c r="AQ7" s="3"/>
-      <c r="AR7" s="10">
+      <c r="AP7" s="2"/>
+      <c r="AQ7" s="2"/>
+      <c r="AR7" s="8">
         <v>0.27</v>
       </c>
-      <c r="AS7" s="10">
+      <c r="AS7" s="8">
         <v>0.8</v>
       </c>
-      <c r="AT7" s="10">
+      <c r="AT7" s="8">
         <v>0.05</v>
       </c>
-      <c r="AU7" s="10">
+      <c r="AU7" s="8">
         <v>0.02</v>
       </c>
-      <c r="AV7" s="10">
+      <c r="AV7" s="8">
         <v>0.1</v>
       </c>
-      <c r="AW7" s="3"/>
-      <c r="AX7" s="10">
+      <c r="AW7" s="2"/>
+      <c r="AX7" s="8">
         <v>0.48</v>
       </c>
-      <c r="AY7" s="10">
+      <c r="AY7" s="8">
         <v>0.49</v>
       </c>
-      <c r="AZ7" s="10">
+      <c r="AZ7" s="8">
         <v>0.31</v>
       </c>
-      <c r="BA7" s="10">
+      <c r="BA7" s="8">
         <v>0.51</v>
       </c>
-      <c r="BB7" s="10">
+      <c r="BB7" s="8">
         <v>0.6</v>
       </c>
-      <c r="BC7" s="10">
+      <c r="BC7" s="8">
         <v>0.5</v>
       </c>
-      <c r="BD7" s="10">
+      <c r="BD7" s="8">
         <v>0.19</v>
       </c>
-      <c r="BE7" s="10">
+      <c r="BE7" s="8">
         <v>0.5</v>
       </c>
-      <c r="BF7" s="10">
+      <c r="BF7" s="8">
         <v>0.55000000000000004</v>
       </c>
-      <c r="BG7" s="4"/>
+      <c r="BG7" s="3"/>
     </row>
     <row r="8" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A8" s="19"/>
-      <c r="B8" s="11" t="s">
+      <c r="A8" s="25"/>
+      <c r="B8" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="L8" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="N8" s="12" t="s">
+      <c r="N8" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="P8" s="12" t="s">
+      <c r="P8" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="Q8" s="12" t="s">
+      <c r="Q8" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="R8" s="12" t="s">
+      <c r="R8" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="S8" s="12" t="s">
+      <c r="S8" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="T8" s="12" t="s">
+      <c r="T8" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="U8" s="12" t="s">
+      <c r="U8" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="V8" s="12" t="s">
+      <c r="V8" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="W8" s="12" t="s">
+      <c r="W8" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="X8" s="12" t="s">
+      <c r="X8" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="Y8" s="12" t="s">
+      <c r="Y8" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="Z8" s="12" t="s">
+      <c r="Z8" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="AA8" s="12" t="s">
+      <c r="AA8" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="AB8" s="12" t="s">
+      <c r="AB8" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="AC8" s="12" t="s">
+      <c r="AC8" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="AD8" s="12" t="s">
+      <c r="AD8" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="AE8" s="12" t="s">
+      <c r="AE8" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="AF8" s="12" t="s">
+      <c r="AF8" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="AG8" s="12" t="s">
+      <c r="AG8" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="AH8" s="12" t="s">
+      <c r="AH8" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="AI8" s="12" t="s">
+      <c r="AI8" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="AJ8" s="12" t="s">
+      <c r="AJ8" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="AK8" s="12"/>
-      <c r="AL8" s="12" t="s">
+      <c r="AK8" s="10"/>
+      <c r="AL8" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="AM8" s="12" t="s">
+      <c r="AM8" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="AN8" s="12" t="s">
+      <c r="AN8" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="AO8" s="12" t="s">
+      <c r="AO8" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="AP8" s="12"/>
-      <c r="AQ8" s="12"/>
-      <c r="AR8" s="12" t="s">
+      <c r="AP8" s="10"/>
+      <c r="AQ8" s="10"/>
+      <c r="AR8" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="AS8" s="12" t="s">
+      <c r="AS8" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="AT8" s="12" t="s">
+      <c r="AT8" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="AU8" s="12" t="s">
+      <c r="AU8" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="AV8" s="12" t="s">
+      <c r="AV8" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="AW8" s="12"/>
-      <c r="AX8" s="12" t="s">
+      <c r="AW8" s="10"/>
+      <c r="AX8" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="AY8" s="12" t="s">
+      <c r="AY8" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="AZ8" s="12" t="s">
+      <c r="AZ8" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="BA8" s="12" t="s">
+      <c r="BA8" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="BB8" s="12" t="s">
+      <c r="BB8" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="BC8" s="12" t="s">
+      <c r="BC8" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="BD8" s="12" t="s">
+      <c r="BD8" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="BE8" s="12" t="s">
+      <c r="BE8" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="BF8" s="12" t="s">
+      <c r="BF8" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="BG8" s="13"/>
+      <c r="BG8" s="11"/>
     </row>
     <row r="9" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="7">
         <v>0.27</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="8">
         <v>0.32</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="7">
         <v>0.22</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="8">
         <v>0.3</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="8">
         <v>0.32</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="8">
         <v>0.67</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="8">
         <v>0.08</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="8">
         <v>0.09</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="8">
         <v>0.31</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="8">
         <v>0.17</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="8">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="8">
         <v>0.24</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="8">
         <v>0.19</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="7">
         <v>0.44</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="8">
         <v>0.37</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="Q9" s="8">
         <v>0.15</v>
       </c>
-      <c r="R9" s="10">
+      <c r="R9" s="8">
         <v>0.43</v>
       </c>
-      <c r="S9" s="10">
+      <c r="S9" s="8">
         <v>0.27</v>
       </c>
-      <c r="T9" s="10">
+      <c r="T9" s="8">
         <v>0.49</v>
       </c>
-      <c r="U9" s="10">
+      <c r="U9" s="8">
         <v>0.94</v>
       </c>
-      <c r="V9" s="10">
+      <c r="V9" s="8">
         <v>0.32</v>
       </c>
-      <c r="W9" s="10">
+      <c r="W9" s="8">
         <v>0.19</v>
       </c>
-      <c r="X9" s="10">
+      <c r="X9" s="8">
         <v>0.21</v>
       </c>
-      <c r="Y9" s="10">
+      <c r="Y9" s="8">
         <v>0.47</v>
       </c>
-      <c r="Z9" s="10">
+      <c r="Z9" s="8">
         <v>0.53</v>
       </c>
-      <c r="AA9" s="10">
+      <c r="AA9" s="8">
         <v>0.7</v>
       </c>
-      <c r="AB9" s="10">
+      <c r="AB9" s="8">
         <v>0.21</v>
       </c>
-      <c r="AC9" s="10">
+      <c r="AC9" s="8">
         <v>0.03</v>
       </c>
-      <c r="AD9" s="10">
+      <c r="AD9" s="8">
         <v>0.06</v>
       </c>
-      <c r="AE9" s="10">
+      <c r="AE9" s="8">
         <v>0.04</v>
       </c>
-      <c r="AF9" s="10">
+      <c r="AF9" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AG9" s="10">
+      <c r="AG9" s="8">
         <v>0.1</v>
       </c>
-      <c r="AH9" s="10">
+      <c r="AH9" s="8">
         <v>0.4</v>
       </c>
-      <c r="AI9" s="10">
+      <c r="AI9" s="8">
         <v>0.45</v>
       </c>
-      <c r="AJ9" s="10">
+      <c r="AJ9" s="8">
         <v>0.12</v>
       </c>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="10">
+      <c r="AK9" s="2"/>
+      <c r="AL9" s="8">
         <v>0.3</v>
       </c>
-      <c r="AM9" s="10">
+      <c r="AM9" s="8">
         <v>0.15</v>
       </c>
-      <c r="AN9" s="10">
+      <c r="AN9" s="8">
         <v>0.05</v>
       </c>
-      <c r="AO9" s="10">
+      <c r="AO9" s="8">
         <v>0.13</v>
       </c>
-      <c r="AP9" s="3"/>
-      <c r="AQ9" s="3"/>
-      <c r="AR9" s="10">
+      <c r="AP9" s="2"/>
+      <c r="AQ9" s="2"/>
+      <c r="AR9" s="8">
         <v>0.41</v>
       </c>
-      <c r="AS9" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AT9" s="10">
+      <c r="AS9" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AT9" s="8">
         <v>0.73</v>
       </c>
-      <c r="AU9" s="10">
+      <c r="AU9" s="8">
         <v>0.38</v>
       </c>
-      <c r="AV9" s="10">
+      <c r="AV9" s="8">
         <v>0.64</v>
       </c>
-      <c r="AW9" s="3"/>
-      <c r="AX9" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AY9" s="10">
+      <c r="AW9" s="2"/>
+      <c r="AX9" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AY9" s="8">
         <v>0.27</v>
       </c>
-      <c r="AZ9" s="10">
+      <c r="AZ9" s="8">
         <v>0.55000000000000004</v>
       </c>
-      <c r="BA9" s="10">
+      <c r="BA9" s="8">
         <v>0.4</v>
       </c>
-      <c r="BB9" s="10">
+      <c r="BB9" s="8">
         <v>0.12</v>
       </c>
-      <c r="BC9" s="10">
+      <c r="BC9" s="8">
         <v>0.08</v>
       </c>
-      <c r="BD9" s="10">
+      <c r="BD9" s="8">
         <v>0.23</v>
       </c>
-      <c r="BE9" s="10">
+      <c r="BE9" s="8">
         <v>0.2</v>
       </c>
-      <c r="BF9" s="10">
+      <c r="BF9" s="8">
         <v>0.28999999999999998</v>
       </c>
-      <c r="BG9" s="4"/>
+      <c r="BG9" s="3"/>
     </row>
     <row r="10" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A10" s="19"/>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="N10" s="12" t="s">
+      <c r="N10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="P10" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="Q10" s="12" t="s">
+      <c r="Q10" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="R10" s="12" t="s">
+      <c r="R10" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="S10" s="12" t="s">
+      <c r="S10" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="T10" s="12" t="s">
+      <c r="T10" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="U10" s="12" t="s">
+      <c r="U10" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="V10" s="12" t="s">
+      <c r="V10" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="W10" s="12" t="s">
+      <c r="W10" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="X10" s="12" t="s">
+      <c r="X10" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="Y10" s="12" t="s">
+      <c r="Y10" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="Z10" s="12" t="s">
+      <c r="Z10" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="AA10" s="12" t="s">
+      <c r="AA10" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="AB10" s="12" t="s">
+      <c r="AB10" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="AC10" s="12" t="s">
+      <c r="AC10" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="AD10" s="12" t="s">
+      <c r="AD10" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="AE10" s="12" t="s">
+      <c r="AE10" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="AF10" s="12" t="s">
+      <c r="AF10" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="AG10" s="12" t="s">
+      <c r="AG10" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="AH10" s="12" t="s">
+      <c r="AH10" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="AI10" s="12" t="s">
+      <c r="AI10" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="AJ10" s="12" t="s">
+      <c r="AJ10" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="AK10" s="12"/>
-      <c r="AL10" s="12" t="s">
+      <c r="AK10" s="10"/>
+      <c r="AL10" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="AM10" s="12" t="s">
+      <c r="AM10" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="AN10" s="12" t="s">
+      <c r="AN10" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="AO10" s="12" t="s">
+      <c r="AO10" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="AP10" s="12"/>
-      <c r="AQ10" s="12"/>
-      <c r="AR10" s="12" t="s">
+      <c r="AP10" s="10"/>
+      <c r="AQ10" s="10"/>
+      <c r="AR10" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="AS10" s="12" t="s">
+      <c r="AS10" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="AT10" s="12" t="s">
+      <c r="AT10" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="AU10" s="12" t="s">
+      <c r="AU10" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="AV10" s="12" t="s">
+      <c r="AV10" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="AW10" s="12"/>
-      <c r="AX10" s="12" t="s">
+      <c r="AW10" s="10"/>
+      <c r="AX10" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="AY10" s="12" t="s">
+      <c r="AY10" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="AZ10" s="12" t="s">
+      <c r="AZ10" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="BA10" s="12" t="s">
+      <c r="BA10" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="BB10" s="12" t="s">
+      <c r="BB10" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="BC10" s="12" t="s">
+      <c r="BC10" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="BD10" s="12" t="s">
+      <c r="BD10" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="BE10" s="12" t="s">
+      <c r="BE10" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="BF10" s="12" t="s">
+      <c r="BF10" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="BG10" s="13"/>
+      <c r="BG10" s="11"/>
     </row>
     <row r="11" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="7">
         <v>0.15</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="8">
         <v>0.04</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="7">
         <v>0.25</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="8">
         <v>0.04</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="8">
         <v>0.05</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="8">
         <v>0.08</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="8">
         <v>0.4</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="8">
         <v>0.24</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="8">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="8">
         <v>0.18</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="8">
         <v>0.03</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="8">
         <v>0.17</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="8">
         <v>0.17</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="7">
         <v>0.19</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="8">
         <v>0.08</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="8">
         <v>0.03</v>
       </c>
-      <c r="R11" s="10">
+      <c r="R11" s="8">
         <v>0.02</v>
       </c>
-      <c r="S11" s="10">
+      <c r="S11" s="8">
         <v>0.04</v>
       </c>
-      <c r="T11" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="U11" s="3"/>
-      <c r="V11" s="10">
+      <c r="T11" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="U11" s="2"/>
+      <c r="V11" s="8">
         <v>0.04</v>
       </c>
-      <c r="W11" s="10">
+      <c r="W11" s="8">
         <v>0.1</v>
       </c>
-      <c r="X11" s="10">
+      <c r="X11" s="8">
         <v>0.02</v>
       </c>
-      <c r="Y11" s="10">
+      <c r="Y11" s="8">
         <v>0.2</v>
       </c>
-      <c r="Z11" s="10">
+      <c r="Z11" s="8">
         <v>0.02</v>
       </c>
-      <c r="AA11" s="10">
+      <c r="AA11" s="8">
         <v>0.04</v>
       </c>
-      <c r="AB11" s="10">
+      <c r="AB11" s="8">
         <v>0.38</v>
       </c>
-      <c r="AC11" s="10">
+      <c r="AC11" s="8">
         <v>0.43</v>
       </c>
-      <c r="AD11" s="10">
+      <c r="AD11" s="8">
         <v>0.42</v>
       </c>
-      <c r="AE11" s="10">
+      <c r="AE11" s="8">
         <v>0.36</v>
       </c>
-      <c r="AF11" s="10">
+      <c r="AF11" s="8">
         <v>0.38</v>
       </c>
-      <c r="AG11" s="10">
+      <c r="AG11" s="8">
         <v>0.21</v>
       </c>
-      <c r="AH11" s="10">
+      <c r="AH11" s="8">
         <v>0.19</v>
       </c>
-      <c r="AI11" s="10">
+      <c r="AI11" s="8">
         <v>0.09</v>
       </c>
-      <c r="AJ11" s="10">
+      <c r="AJ11" s="8">
         <v>0.13</v>
       </c>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="10">
+      <c r="AK11" s="2"/>
+      <c r="AL11" s="8">
         <v>0.11</v>
       </c>
-      <c r="AM11" s="10">
+      <c r="AM11" s="8">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AN11" s="10">
+      <c r="AN11" s="8">
         <v>0.28000000000000003</v>
       </c>
-      <c r="AO11" s="10">
+      <c r="AO11" s="8">
         <v>0.46</v>
       </c>
-      <c r="AP11" s="3"/>
-      <c r="AQ11" s="3"/>
-      <c r="AR11" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AS11" s="10">
+      <c r="AP11" s="2"/>
+      <c r="AQ11" s="2"/>
+      <c r="AR11" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AS11" s="8">
         <v>0.04</v>
       </c>
-      <c r="AT11" s="10">
+      <c r="AT11" s="8">
         <v>0.11</v>
       </c>
-      <c r="AU11" s="10">
+      <c r="AU11" s="8">
         <v>0.32</v>
       </c>
-      <c r="AV11" s="10">
+      <c r="AV11" s="8">
         <v>0.15</v>
       </c>
-      <c r="AW11" s="3"/>
-      <c r="AX11" s="10">
+      <c r="AW11" s="2"/>
+      <c r="AX11" s="8">
         <v>0</v>
       </c>
-      <c r="AY11" s="10">
+      <c r="AY11" s="8">
         <v>0.05</v>
       </c>
-      <c r="AZ11" s="10">
+      <c r="AZ11" s="8">
         <v>0.09</v>
       </c>
-      <c r="BA11" s="10">
+      <c r="BA11" s="8">
         <v>0.03</v>
       </c>
-      <c r="BB11" s="10">
+      <c r="BB11" s="8">
         <v>0.09</v>
       </c>
-      <c r="BC11" s="10">
+      <c r="BC11" s="8">
         <v>0.21</v>
       </c>
-      <c r="BD11" s="10">
+      <c r="BD11" s="8">
         <v>0.25</v>
       </c>
-      <c r="BE11" s="10">
+      <c r="BE11" s="8">
         <v>0.04</v>
       </c>
-      <c r="BF11" s="3"/>
-      <c r="BG11" s="4"/>
+      <c r="BF11" s="2"/>
+      <c r="BG11" s="3"/>
     </row>
     <row r="12" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A12" s="19"/>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="25"/>
+      <c r="B12" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="L12" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="N12" s="12" t="s">
+      <c r="N12" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="P12" s="12" t="s">
+      <c r="P12" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="Q12" s="12" t="s">
+      <c r="Q12" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="R12" s="12" t="s">
+      <c r="R12" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="S12" s="12" t="s">
+      <c r="S12" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="T12" s="12" t="s">
+      <c r="T12" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="U12" s="12" t="s">
+      <c r="U12" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="V12" s="12" t="s">
+      <c r="V12" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="W12" s="12" t="s">
+      <c r="W12" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="X12" s="12" t="s">
+      <c r="X12" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="Y12" s="12" t="s">
+      <c r="Y12" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="Z12" s="12" t="s">
+      <c r="Z12" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="AA12" s="12" t="s">
+      <c r="AA12" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="AB12" s="12" t="s">
+      <c r="AB12" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="AC12" s="12" t="s">
+      <c r="AC12" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="AD12" s="12" t="s">
+      <c r="AD12" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="AE12" s="12" t="s">
+      <c r="AE12" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="AF12" s="12" t="s">
+      <c r="AF12" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="AG12" s="12" t="s">
+      <c r="AG12" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="AH12" s="12" t="s">
+      <c r="AH12" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="AI12" s="12" t="s">
+      <c r="AI12" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="AJ12" s="12" t="s">
+      <c r="AJ12" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="AK12" s="12"/>
-      <c r="AL12" s="12" t="s">
+      <c r="AK12" s="10"/>
+      <c r="AL12" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="AM12" s="12" t="s">
+      <c r="AM12" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="AN12" s="12" t="s">
+      <c r="AN12" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="AO12" s="12" t="s">
+      <c r="AO12" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="AP12" s="12"/>
-      <c r="AQ12" s="12"/>
-      <c r="AR12" s="12" t="s">
+      <c r="AP12" s="10"/>
+      <c r="AQ12" s="10"/>
+      <c r="AR12" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="AS12" s="12" t="s">
+      <c r="AS12" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="AT12" s="12" t="s">
+      <c r="AT12" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="AU12" s="12" t="s">
+      <c r="AU12" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="AV12" s="12" t="s">
+      <c r="AV12" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="AW12" s="12"/>
-      <c r="AX12" s="12" t="s">
+      <c r="AW12" s="10"/>
+      <c r="AX12" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="AY12" s="12" t="s">
+      <c r="AY12" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="AZ12" s="12" t="s">
+      <c r="AZ12" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="BA12" s="12" t="s">
+      <c r="BA12" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="BB12" s="12" t="s">
+      <c r="BB12" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="BC12" s="12" t="s">
+      <c r="BC12" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="BD12" s="12" t="s">
+      <c r="BD12" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="BE12" s="12" t="s">
+      <c r="BE12" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="BF12" s="12" t="s">
+      <c r="BF12" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="BG12" s="13"/>
+      <c r="BG12" s="11"/>
     </row>
     <row r="13" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="7">
         <v>0.09</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="8">
         <v>0.12</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="7">
         <v>0.06</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="8">
         <v>0.1</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="8">
         <v>0.15</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="8">
         <v>0.03</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="8">
         <v>0.02</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="8">
         <v>0.06</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="8">
         <v>0.06</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="8">
         <v>0.08</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="8">
         <v>0.08</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="8">
         <v>0.03</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="8">
         <v>0.19</v>
       </c>
-      <c r="O13" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="P13" s="10">
+      <c r="O13" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="P13" s="8">
         <v>0.11</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="Q13" s="8">
         <v>0.13</v>
       </c>
-      <c r="R13" s="10">
+      <c r="R13" s="8">
         <v>0.12</v>
       </c>
-      <c r="S13" s="10">
+      <c r="S13" s="8">
         <v>0.11</v>
       </c>
-      <c r="T13" s="10">
+      <c r="T13" s="8">
         <v>0.03</v>
       </c>
-      <c r="U13" s="10">
+      <c r="U13" s="8">
         <v>0</v>
       </c>
-      <c r="V13" s="10">
+      <c r="V13" s="8">
         <v>0.12</v>
       </c>
-      <c r="W13" s="10">
+      <c r="W13" s="8">
         <v>0.19</v>
       </c>
-      <c r="X13" s="10">
+      <c r="X13" s="8">
         <v>0.21</v>
       </c>
-      <c r="Y13" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="Z13" s="10">
+      <c r="Y13" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="Z13" s="8">
         <v>0.05</v>
       </c>
-      <c r="AA13" s="10">
+      <c r="AA13" s="8">
         <v>0.05</v>
       </c>
-      <c r="AB13" s="10">
+      <c r="AB13" s="8">
         <v>0.05</v>
       </c>
-      <c r="AC13" s="10">
+      <c r="AC13" s="8">
         <v>0.02</v>
       </c>
-      <c r="AD13" s="10">
+      <c r="AD13" s="8">
         <v>0.02</v>
       </c>
-      <c r="AE13" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="10">
+      <c r="AE13" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AF13" s="2"/>
+      <c r="AG13" s="8">
         <v>0.08</v>
       </c>
-      <c r="AH13" s="10">
+      <c r="AH13" s="8">
         <v>0.1</v>
       </c>
-      <c r="AI13" s="10">
+      <c r="AI13" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ13" s="10">
+      <c r="AJ13" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="10">
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="10">
+      <c r="AM13" s="2"/>
+      <c r="AN13" s="8">
         <v>0.15</v>
       </c>
-      <c r="AO13" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AP13" s="3"/>
-      <c r="AQ13" s="3"/>
-      <c r="AR13" s="10">
+      <c r="AO13" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AP13" s="2"/>
+      <c r="AQ13" s="2"/>
+      <c r="AR13" s="8">
         <v>0.03</v>
       </c>
-      <c r="AS13" s="10">
+      <c r="AS13" s="8">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AT13" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AU13" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AV13" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AW13" s="3"/>
-      <c r="AX13" s="10">
+      <c r="AT13" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AU13" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AV13" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AW13" s="2"/>
+      <c r="AX13" s="8">
         <v>0.11</v>
       </c>
-      <c r="AY13" s="3"/>
-      <c r="AZ13" s="10">
+      <c r="AY13" s="2"/>
+      <c r="AZ13" s="8">
         <v>0</v>
       </c>
-      <c r="BA13" s="3"/>
-      <c r="BB13" s="10">
+      <c r="BA13" s="2"/>
+      <c r="BB13" s="8">
         <v>0.14000000000000001</v>
       </c>
-      <c r="BC13" s="10">
+      <c r="BC13" s="8">
         <v>0.03</v>
       </c>
-      <c r="BD13" s="10">
+      <c r="BD13" s="8">
         <v>0.31</v>
       </c>
-      <c r="BE13" s="10">
+      <c r="BE13" s="8">
         <v>0.02</v>
       </c>
-      <c r="BF13" s="10">
+      <c r="BF13" s="8">
         <v>0.16</v>
       </c>
-      <c r="BG13" s="4"/>
+      <c r="BG13" s="3"/>
     </row>
     <row r="14" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A14" s="19"/>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="L14" s="12" t="s">
+      <c r="L14" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="N14" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="P14" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="Q14" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="R14" s="12" t="s">
+      <c r="R14" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12" t="s">
+      <c r="S14" s="10"/>
+      <c r="T14" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="U14" s="12" t="s">
+      <c r="U14" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="V14" s="12" t="s">
+      <c r="V14" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="W14" s="12" t="s">
+      <c r="W14" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="X14" s="12" t="s">
+      <c r="X14" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="Y14" s="12" t="s">
+      <c r="Y14" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="Z14" s="12" t="s">
+      <c r="Z14" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="AA14" s="12" t="s">
+      <c r="AA14" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="AB14" s="12" t="s">
+      <c r="AB14" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="AC14" s="12" t="s">
+      <c r="AC14" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="AD14" s="12" t="s">
+      <c r="AD14" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="AE14" s="12" t="s">
+      <c r="AE14" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="AF14" s="12" t="s">
+      <c r="AF14" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="AG14" s="12" t="s">
+      <c r="AG14" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="AH14" s="12" t="s">
+      <c r="AH14" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="AI14" s="12" t="s">
+      <c r="AI14" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="AJ14" s="12" t="s">
+      <c r="AJ14" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="AK14" s="12"/>
-      <c r="AL14" s="12" t="s">
+      <c r="AK14" s="10"/>
+      <c r="AL14" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="AM14" s="12" t="s">
+      <c r="AM14" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="AN14" s="12" t="s">
+      <c r="AN14" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="AO14" s="12" t="s">
+      <c r="AO14" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="AP14" s="12"/>
-      <c r="AQ14" s="12"/>
-      <c r="AR14" s="12" t="s">
+      <c r="AP14" s="10"/>
+      <c r="AQ14" s="10"/>
+      <c r="AR14" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="AS14" s="12" t="s">
+      <c r="AS14" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="AT14" s="12" t="s">
+      <c r="AT14" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="AU14" s="12" t="s">
+      <c r="AU14" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="AV14" s="12" t="s">
+      <c r="AV14" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="AW14" s="12"/>
-      <c r="AX14" s="12" t="s">
+      <c r="AW14" s="10"/>
+      <c r="AX14" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="AY14" s="12" t="s">
+      <c r="AY14" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="AZ14" s="12" t="s">
+      <c r="AZ14" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="BA14" s="12"/>
-      <c r="BB14" s="12" t="s">
+      <c r="BA14" s="10"/>
+      <c r="BB14" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="BC14" s="12" t="s">
+      <c r="BC14" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="BD14" s="12" t="s">
+      <c r="BD14" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="BE14" s="12" t="s">
+      <c r="BE14" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="BF14" s="12" t="s">
+      <c r="BF14" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="BG14" s="13"/>
+      <c r="BG14" s="11"/>
     </row>
     <row r="15" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="7">
         <v>0.05</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="8">
         <v>0.03</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="7">
         <v>0.06</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="8">
         <v>0.04</v>
       </c>
-      <c r="F15" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="G15" s="10">
+      <c r="F15" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="G15" s="8">
         <v>0.02</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="8">
         <v>0.09</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="8">
         <v>0.12</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="8">
         <v>0.02</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="8">
         <v>0.11</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="8">
         <v>0</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="8">
         <v>0.02</v>
       </c>
-      <c r="O15" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="P15" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="R15" s="10">
+      <c r="O15" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="R15" s="8">
         <v>0</v>
       </c>
-      <c r="S15" s="10">
+      <c r="S15" s="8">
         <v>0.03</v>
       </c>
-      <c r="T15" s="10">
+      <c r="T15" s="8">
         <v>0.24</v>
       </c>
-      <c r="U15" s="10">
+      <c r="U15" s="8">
         <v>0</v>
       </c>
-      <c r="V15" s="3"/>
-      <c r="W15" s="10">
+      <c r="V15" s="2"/>
+      <c r="W15" s="8">
         <v>0.03</v>
       </c>
-      <c r="X15" s="10">
+      <c r="X15" s="8">
         <v>0</v>
       </c>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="10">
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="8">
         <v>0.02</v>
       </c>
-      <c r="AB15" s="10">
+      <c r="AB15" s="8">
         <v>0.02</v>
       </c>
-      <c r="AC15" s="10">
+      <c r="AC15" s="8">
         <v>0.17</v>
       </c>
-      <c r="AD15" s="10">
+      <c r="AD15" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AE15" s="10">
+      <c r="AE15" s="8">
         <v>0.17</v>
       </c>
-      <c r="AF15" s="10">
+      <c r="AF15" s="8">
         <v>0.17</v>
       </c>
-      <c r="AG15" s="10">
+      <c r="AG15" s="8">
         <v>0.11</v>
       </c>
-      <c r="AH15" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AI15" s="10">
+      <c r="AH15" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AI15" s="8">
         <v>0.03</v>
       </c>
-      <c r="AJ15" s="10">
+      <c r="AJ15" s="8">
         <v>0</v>
       </c>
-      <c r="AK15" s="3"/>
-      <c r="AL15" s="10">
+      <c r="AK15" s="2"/>
+      <c r="AL15" s="8">
         <v>0.03</v>
       </c>
-      <c r="AM15" s="10">
+      <c r="AM15" s="8">
         <v>0.1</v>
       </c>
-      <c r="AN15" s="10">
+      <c r="AN15" s="8">
         <v>0.2</v>
       </c>
-      <c r="AO15" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AP15" s="3"/>
-      <c r="AQ15" s="3"/>
-      <c r="AR15" s="10">
+      <c r="AO15" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AP15" s="2"/>
+      <c r="AQ15" s="2"/>
+      <c r="AR15" s="8">
         <v>0</v>
       </c>
-      <c r="AS15" s="3"/>
-      <c r="AT15" s="10">
+      <c r="AS15" s="2"/>
+      <c r="AT15" s="8">
         <v>0.02</v>
       </c>
-      <c r="AU15" s="10">
+      <c r="AU15" s="8">
         <v>0.12</v>
       </c>
-      <c r="AV15" s="10">
+      <c r="AV15" s="8">
         <v>0.03</v>
       </c>
-      <c r="AW15" s="3"/>
-      <c r="AX15" s="10">
+      <c r="AW15" s="2"/>
+      <c r="AX15" s="8">
         <v>0.08</v>
       </c>
-      <c r="AY15" s="10">
+      <c r="AY15" s="8">
         <v>0.03</v>
       </c>
-      <c r="AZ15" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="BA15" s="10">
+      <c r="AZ15" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="BA15" s="8">
         <v>0</v>
       </c>
-      <c r="BB15" s="3"/>
-      <c r="BC15" s="3"/>
-      <c r="BD15" s="10">
+      <c r="BB15" s="2"/>
+      <c r="BC15" s="2"/>
+      <c r="BD15" s="8">
         <v>0</v>
       </c>
-      <c r="BE15" s="10">
+      <c r="BE15" s="8">
         <v>0.16</v>
       </c>
-      <c r="BF15" s="10">
+      <c r="BF15" s="8">
         <v>0</v>
       </c>
-      <c r="BG15" s="4"/>
+      <c r="BG15" s="3"/>
     </row>
     <row r="16" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A16" s="19"/>
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="25"/>
+      <c r="B16" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="K16" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="L16" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="N16" s="12" t="s">
+      <c r="N16" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="P16" s="12" t="s">
+      <c r="P16" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="Q16" s="12" t="s">
+      <c r="Q16" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="R16" s="12" t="s">
+      <c r="R16" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12" t="s">
+      <c r="S16" s="10"/>
+      <c r="T16" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="U16" s="12" t="s">
+      <c r="U16" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="V16" s="12" t="s">
+      <c r="V16" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="W16" s="12" t="s">
+      <c r="W16" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="X16" s="12" t="s">
+      <c r="X16" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="Y16" s="12"/>
-      <c r="Z16" s="12" t="s">
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="AA16" s="12" t="s">
+      <c r="AA16" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="AB16" s="12" t="s">
+      <c r="AB16" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="AC16" s="12" t="s">
+      <c r="AC16" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="AD16" s="12" t="s">
+      <c r="AD16" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="AE16" s="12" t="s">
+      <c r="AE16" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="AF16" s="12" t="s">
+      <c r="AF16" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="AG16" s="12" t="s">
+      <c r="AG16" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="AH16" s="12" t="s">
+      <c r="AH16" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="AI16" s="12" t="s">
+      <c r="AI16" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="AJ16" s="12" t="s">
+      <c r="AJ16" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="AK16" s="12"/>
-      <c r="AL16" s="12" t="s">
+      <c r="AK16" s="10"/>
+      <c r="AL16" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="AM16" s="12" t="s">
+      <c r="AM16" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="AN16" s="12" t="s">
+      <c r="AN16" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="AO16" s="12" t="s">
+      <c r="AO16" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="AP16" s="12"/>
-      <c r="AQ16" s="12"/>
-      <c r="AR16" s="12" t="s">
+      <c r="AP16" s="10"/>
+      <c r="AQ16" s="10"/>
+      <c r="AR16" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="AS16" s="12" t="s">
+      <c r="AS16" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="AT16" s="12" t="s">
+      <c r="AT16" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="AU16" s="12" t="s">
+      <c r="AU16" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="AV16" s="12" t="s">
+      <c r="AV16" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="AW16" s="12"/>
-      <c r="AX16" s="12" t="s">
+      <c r="AW16" s="10"/>
+      <c r="AX16" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="AY16" s="12" t="s">
+      <c r="AY16" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="AZ16" s="12" t="s">
+      <c r="AZ16" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="BA16" s="12"/>
-      <c r="BB16" s="12" t="s">
+      <c r="BA16" s="10"/>
+      <c r="BB16" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="BC16" s="12" t="s">
+      <c r="BC16" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="BD16" s="12" t="s">
+      <c r="BD16" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="BE16" s="12" t="s">
+      <c r="BE16" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="BF16" s="12"/>
-      <c r="BG16" s="13"/>
+      <c r="BF16" s="10"/>
+      <c r="BG16" s="11"/>
     </row>
     <row r="17" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="7">
         <v>0.03</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="8">
         <v>0.05</v>
       </c>
-      <c r="D17" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="E17" s="10">
+      <c r="D17" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="E17" s="8">
         <v>0.04</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="8">
         <v>0.08</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="8">
         <v>0.04</v>
       </c>
-      <c r="H17" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="I17" s="10">
+      <c r="H17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="I17" s="8">
         <v>0.02</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="8">
         <v>0.02</v>
       </c>
-      <c r="K17" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="L17" s="10">
+      <c r="K17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="L17" s="8">
         <v>0.04</v>
       </c>
-      <c r="M17" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="N17" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="O17" s="9">
+      <c r="M17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="O17" s="7">
         <v>0</v>
       </c>
-      <c r="P17" s="10">
+      <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="Q17" s="8">
         <v>0.05</v>
       </c>
-      <c r="R17" s="10">
+      <c r="R17" s="8">
         <v>0.06</v>
       </c>
-      <c r="S17" s="10">
+      <c r="S17" s="8">
         <v>0.37</v>
       </c>
-      <c r="T17" s="10">
+      <c r="T17" s="8">
         <v>0</v>
       </c>
-      <c r="U17" s="3"/>
-      <c r="V17" s="10">
+      <c r="U17" s="2"/>
+      <c r="V17" s="8">
         <v>0.08</v>
       </c>
-      <c r="W17" s="10">
+      <c r="W17" s="8">
         <v>0.08</v>
       </c>
-      <c r="X17" s="10">
+      <c r="X17" s="8">
         <v>0.13</v>
       </c>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="10">
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="8">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AA17" s="10">
+      <c r="AA17" s="8">
         <v>0.02</v>
       </c>
-      <c r="AB17" s="10">
+      <c r="AB17" s="8">
         <v>0</v>
       </c>
-      <c r="AC17" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AD17" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AE17" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AF17" s="3"/>
-      <c r="AG17" s="10">
+      <c r="AC17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AD17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AE17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AF17" s="2"/>
+      <c r="AG17" s="8">
         <v>0.02</v>
       </c>
-      <c r="AH17" s="3"/>
-      <c r="AI17" s="10">
+      <c r="AH17" s="2"/>
+      <c r="AI17" s="8">
         <v>0.03</v>
       </c>
-      <c r="AJ17" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AK17" s="3"/>
-      <c r="AL17" s="10">
+      <c r="AJ17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AK17" s="2"/>
+      <c r="AL17" s="8">
         <v>0.02</v>
       </c>
-      <c r="AM17" s="10">
+      <c r="AM17" s="8">
         <v>0</v>
       </c>
-      <c r="AN17" s="3"/>
-      <c r="AO17" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AP17" s="3"/>
-      <c r="AQ17" s="3"/>
-      <c r="AR17" s="10">
+      <c r="AN17" s="2"/>
+      <c r="AO17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AP17" s="2"/>
+      <c r="AQ17" s="2"/>
+      <c r="AR17" s="8">
         <v>0.06</v>
       </c>
-      <c r="AS17" s="3"/>
-      <c r="AT17" s="10">
+      <c r="AS17" s="2"/>
+      <c r="AT17" s="8">
         <v>0.02</v>
       </c>
-      <c r="AU17" s="3"/>
-      <c r="AV17" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AW17" s="3"/>
-      <c r="AX17" s="10">
+      <c r="AU17" s="2"/>
+      <c r="AV17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AW17" s="2"/>
+      <c r="AX17" s="8">
         <v>0.06</v>
       </c>
-      <c r="AY17" s="3"/>
-      <c r="AZ17" s="3"/>
-      <c r="BA17" s="3"/>
-      <c r="BB17" s="10">
+      <c r="AY17" s="2"/>
+      <c r="AZ17" s="2"/>
+      <c r="BA17" s="2"/>
+      <c r="BB17" s="8">
         <v>0.04</v>
       </c>
-      <c r="BC17" s="3"/>
-      <c r="BD17" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="BE17" s="10">
+      <c r="BC17" s="2"/>
+      <c r="BD17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="BE17" s="8">
         <v>0</v>
       </c>
-      <c r="BF17" s="3"/>
-      <c r="BG17" s="4"/>
+      <c r="BF17" s="2"/>
+      <c r="BG17" s="3"/>
     </row>
     <row r="18" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A18" s="19"/>
-      <c r="B18" s="11" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12" t="s">
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L18" s="12" t="s">
+      <c r="L18" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12" t="s">
+      <c r="M18" s="10"/>
+      <c r="N18" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="O18" s="11"/>
-      <c r="P18" s="12" t="s">
+      <c r="O18" s="9"/>
+      <c r="P18" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="Q18" s="12" t="s">
+      <c r="Q18" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="R18" s="12" t="s">
+      <c r="R18" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="S18" s="12" t="s">
+      <c r="S18" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="T18" s="12" t="s">
+      <c r="T18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="U18" s="12" t="s">
+      <c r="U18" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="V18" s="12" t="s">
+      <c r="V18" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="W18" s="12" t="s">
+      <c r="W18" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="X18" s="12" t="s">
+      <c r="X18" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="Y18" s="12"/>
-      <c r="Z18" s="12" t="s">
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="AA18" s="12" t="s">
+      <c r="AA18" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="AB18" s="12" t="s">
+      <c r="AB18" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="AC18" s="12" t="s">
+      <c r="AC18" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="AD18" s="12" t="s">
+      <c r="AD18" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="AE18" s="12" t="s">
+      <c r="AE18" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="AF18" s="12" t="s">
+      <c r="AF18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AG18" s="12" t="s">
+      <c r="AG18" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="AH18" s="12" t="s">
+      <c r="AH18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AI18" s="12" t="s">
+      <c r="AI18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AJ18" s="12" t="s">
+      <c r="AJ18" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="AK18" s="12"/>
-      <c r="AL18" s="12" t="s">
+      <c r="AK18" s="10"/>
+      <c r="AL18" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="AM18" s="12" t="s">
+      <c r="AM18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AN18" s="12" t="s">
+      <c r="AN18" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="AO18" s="12" t="s">
+      <c r="AO18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AP18" s="12"/>
-      <c r="AQ18" s="12"/>
-      <c r="AR18" s="12" t="s">
+      <c r="AP18" s="10"/>
+      <c r="AQ18" s="10"/>
+      <c r="AR18" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="AS18" s="12" t="s">
+      <c r="AS18" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="AT18" s="12" t="s">
+      <c r="AT18" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="AU18" s="12" t="s">
+      <c r="AU18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AV18" s="12" t="s">
+      <c r="AV18" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="AW18" s="12"/>
-      <c r="AX18" s="12"/>
-      <c r="AY18" s="12"/>
-      <c r="AZ18" s="12" t="s">
+      <c r="AW18" s="10"/>
+      <c r="AX18" s="10"/>
+      <c r="AY18" s="10"/>
+      <c r="AZ18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="BA18" s="12"/>
-      <c r="BB18" s="12" t="s">
+      <c r="BA18" s="10"/>
+      <c r="BB18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="BC18" s="12" t="s">
+      <c r="BC18" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="BD18" s="12" t="s">
+      <c r="BD18" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="BE18" s="12" t="s">
+      <c r="BE18" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="BF18" s="12"/>
-      <c r="BG18" s="13"/>
+      <c r="BF18" s="10"/>
+      <c r="BG18" s="11"/>
     </row>
     <row r="19" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="7">
         <v>0.02</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="8">
         <v>0</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="7">
         <v>0.03</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="8">
         <v>0</v>
       </c>
-      <c r="F19" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="G19" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="H19" s="10">
+      <c r="F19" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="H19" s="8">
         <v>0.02</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="8">
         <v>0.03</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="8">
         <v>0.16</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="8">
         <v>0.03</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="8">
         <v>0.06</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="8">
         <v>0.04</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="8">
         <v>0</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="7">
         <v>0</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="8">
         <v>0</v>
       </c>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="10">
+      <c r="Q19" s="2"/>
+      <c r="R19" s="8">
         <v>0.02</v>
       </c>
-      <c r="S19" s="10">
+      <c r="S19" s="8">
         <v>0.02</v>
       </c>
-      <c r="T19" s="3"/>
-      <c r="U19" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="V19" s="10">
+      <c r="T19" s="2"/>
+      <c r="U19" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="V19" s="8">
         <v>0.02</v>
       </c>
-      <c r="W19" s="10">
+      <c r="W19" s="8">
         <v>0</v>
       </c>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="10">
+      <c r="X19" s="2"/>
+      <c r="Y19" s="8">
         <v>0.04</v>
       </c>
-      <c r="Z19" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AA19" s="10">
+      <c r="Z19" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AA19" s="8">
         <v>0</v>
       </c>
-      <c r="AB19" s="10">
+      <c r="AB19" s="8">
         <v>0</v>
       </c>
-      <c r="AC19" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AD19" s="10">
+      <c r="AC19" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AD19" s="8">
         <v>0.02</v>
       </c>
-      <c r="AE19" s="10">
+      <c r="AE19" s="8">
         <v>0.03</v>
       </c>
-      <c r="AF19" s="10">
+      <c r="AF19" s="8">
         <v>0.03</v>
       </c>
-      <c r="AG19" s="10">
+      <c r="AG19" s="8">
         <v>0.04</v>
       </c>
-      <c r="AH19" s="10">
+      <c r="AH19" s="8">
         <v>0.15</v>
       </c>
-      <c r="AI19" s="10">
+      <c r="AI19" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AJ19" s="10">
+      <c r="AJ19" s="8">
         <v>0.3</v>
       </c>
-      <c r="AK19" s="3"/>
-      <c r="AL19" s="10">
+      <c r="AK19" s="2"/>
+      <c r="AL19" s="8">
         <v>0</v>
       </c>
-      <c r="AM19" s="10">
+      <c r="AM19" s="8">
         <v>0.17</v>
       </c>
-      <c r="AN19" s="10">
+      <c r="AN19" s="8">
         <v>0</v>
       </c>
-      <c r="AO19" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AP19" s="3"/>
-      <c r="AQ19" s="3"/>
-      <c r="AR19" s="10">
+      <c r="AO19" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AP19" s="2"/>
+      <c r="AQ19" s="2"/>
+      <c r="AR19" s="8">
         <v>0.09</v>
       </c>
-      <c r="AS19" s="3"/>
-      <c r="AT19" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AU19" s="3"/>
-      <c r="AV19" s="3"/>
-      <c r="AW19" s="3"/>
-      <c r="AX19" s="10">
+      <c r="AS19" s="2"/>
+      <c r="AT19" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AU19" s="2"/>
+      <c r="AV19" s="2"/>
+      <c r="AW19" s="2"/>
+      <c r="AX19" s="8">
         <v>0.13</v>
       </c>
-      <c r="AY19" s="3"/>
-      <c r="AZ19" s="3"/>
-      <c r="BA19" s="10">
+      <c r="AY19" s="2"/>
+      <c r="AZ19" s="2"/>
+      <c r="BA19" s="8">
         <v>0</v>
       </c>
-      <c r="BB19" s="3"/>
-      <c r="BC19" s="3"/>
-      <c r="BD19" s="3"/>
-      <c r="BE19" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="BF19" s="3"/>
-      <c r="BG19" s="4"/>
+      <c r="BB19" s="2"/>
+      <c r="BC19" s="2"/>
+      <c r="BD19" s="2"/>
+      <c r="BE19" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="BF19" s="2"/>
+      <c r="BG19" s="3"/>
     </row>
     <row r="20" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A20" s="19"/>
-      <c r="B20" s="11" t="s">
+      <c r="A20" s="25"/>
+      <c r="B20" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="K20" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="L20" s="12" t="s">
+      <c r="L20" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="M20" s="12" t="s">
+      <c r="M20" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="N20" s="12" t="s">
+      <c r="N20" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="O20" s="11" t="s">
+      <c r="O20" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="P20" s="12" t="s">
+      <c r="P20" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="Q20" s="12" t="s">
+      <c r="Q20" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="R20" s="12" t="s">
+      <c r="R20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="S20" s="12"/>
-      <c r="T20" s="12" t="s">
+      <c r="S20" s="10"/>
+      <c r="T20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="U20" s="12" t="s">
+      <c r="U20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="V20" s="12" t="s">
+      <c r="V20" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="W20" s="12" t="s">
+      <c r="W20" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="X20" s="12" t="s">
+      <c r="X20" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="Y20" s="12"/>
-      <c r="Z20" s="12" t="s">
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AA20" s="12" t="s">
+      <c r="AA20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AB20" s="12" t="s">
+      <c r="AB20" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="AC20" s="12" t="s">
+      <c r="AC20" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="AD20" s="12" t="s">
+      <c r="AD20" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="AE20" s="12" t="s">
+      <c r="AE20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AF20" s="12" t="s">
+      <c r="AF20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AG20" s="12" t="s">
+      <c r="AG20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AH20" s="12"/>
-      <c r="AI20" s="12" t="s">
+      <c r="AH20" s="10"/>
+      <c r="AI20" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="AJ20" s="12" t="s">
+      <c r="AJ20" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="AK20" s="12"/>
-      <c r="AL20" s="12" t="s">
+      <c r="AK20" s="10"/>
+      <c r="AL20" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="AM20" s="12"/>
-      <c r="AN20" s="12" t="s">
+      <c r="AM20" s="10"/>
+      <c r="AN20" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="AO20" s="12"/>
-      <c r="AP20" s="12"/>
-      <c r="AQ20" s="12"/>
-      <c r="AR20" s="12" t="s">
+      <c r="AO20" s="10"/>
+      <c r="AP20" s="10"/>
+      <c r="AQ20" s="10"/>
+      <c r="AR20" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="AS20" s="12"/>
-      <c r="AT20" s="12" t="s">
+      <c r="AS20" s="10"/>
+      <c r="AT20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AU20" s="12"/>
-      <c r="AV20" s="12" t="s">
+      <c r="AU20" s="10"/>
+      <c r="AV20" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="AW20" s="12"/>
-      <c r="AX20" s="12"/>
-      <c r="AY20" s="12"/>
-      <c r="AZ20" s="12" t="s">
+      <c r="AW20" s="10"/>
+      <c r="AX20" s="10"/>
+      <c r="AY20" s="10"/>
+      <c r="AZ20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="BA20" s="12"/>
-      <c r="BB20" s="12" t="s">
+      <c r="BA20" s="10"/>
+      <c r="BB20" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="BC20" s="12"/>
-      <c r="BD20" s="12" t="s">
+      <c r="BC20" s="10"/>
+      <c r="BD20" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="BE20" s="12"/>
-      <c r="BF20" s="12"/>
-      <c r="BG20" s="13"/>
+      <c r="BE20" s="10"/>
+      <c r="BF20" s="10"/>
+      <c r="BG20" s="11"/>
     </row>
     <row r="21" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="25" t="s">
         <v>339</v>
       </c>
-      <c r="B21" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="C21" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="D21" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="F21" s="10">
+      <c r="B21" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="F21" s="8">
         <v>0.02</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="8">
         <v>0.03</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="8">
         <v>0</v>
       </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="K21" s="10">
+      <c r="I21" s="2"/>
+      <c r="J21" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="K21" s="8">
         <v>0</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="8">
         <v>0</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="8">
         <v>0</v>
       </c>
-      <c r="N21" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="O21" s="9">
+      <c r="N21" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="O21" s="7">
         <v>0</v>
       </c>
-      <c r="P21" s="10">
+      <c r="P21" s="8">
         <v>0</v>
       </c>
-      <c r="Q21" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="R21" s="10">
+      <c r="Q21" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="R21" s="8">
         <v>0</v>
       </c>
-      <c r="S21" s="10">
+      <c r="S21" s="8">
         <v>0.03</v>
       </c>
-      <c r="T21" s="10">
+      <c r="T21" s="8">
         <v>0</v>
       </c>
-      <c r="U21" s="10">
+      <c r="U21" s="8">
         <v>0</v>
       </c>
-      <c r="V21" s="10">
+      <c r="V21" s="8">
         <v>0.03</v>
       </c>
-      <c r="W21" s="10">
+      <c r="W21" s="8">
         <v>0.03</v>
       </c>
-      <c r="X21" s="10">
+      <c r="X21" s="8">
         <v>0</v>
       </c>
-      <c r="Y21" s="10">
+      <c r="Y21" s="8">
         <v>0.08</v>
       </c>
-      <c r="Z21" s="10">
+      <c r="Z21" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AA21" s="3"/>
-      <c r="AB21" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AC21" s="3"/>
-      <c r="AD21" s="10">
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AC21" s="2"/>
+      <c r="AD21" s="8">
         <v>0</v>
       </c>
-      <c r="AE21" s="10">
+      <c r="AE21" s="8">
         <v>0</v>
       </c>
-      <c r="AF21" s="3"/>
-      <c r="AG21" s="3"/>
-      <c r="AH21" s="3"/>
-      <c r="AI21" s="3"/>
-      <c r="AJ21" s="10">
+      <c r="AF21" s="2"/>
+      <c r="AG21" s="2"/>
+      <c r="AH21" s="2"/>
+      <c r="AI21" s="2"/>
+      <c r="AJ21" s="8">
         <v>0.03</v>
       </c>
-      <c r="AK21" s="3"/>
-      <c r="AL21" s="3"/>
-      <c r="AM21" s="3"/>
-      <c r="AN21" s="10">
+      <c r="AK21" s="2"/>
+      <c r="AL21" s="2"/>
+      <c r="AM21" s="2"/>
+      <c r="AN21" s="8">
         <v>0</v>
       </c>
-      <c r="AO21" s="3"/>
-      <c r="AP21" s="3"/>
-      <c r="AQ21" s="3"/>
-      <c r="AR21" s="10">
+      <c r="AO21" s="2"/>
+      <c r="AP21" s="2"/>
+      <c r="AQ21" s="2"/>
+      <c r="AR21" s="8">
         <v>0</v>
       </c>
-      <c r="AS21" s="3"/>
-      <c r="AT21" s="10">
+      <c r="AS21" s="2"/>
+      <c r="AT21" s="8">
         <v>0.02</v>
       </c>
-      <c r="AU21" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AV21" s="3"/>
-      <c r="AW21" s="3"/>
-      <c r="AX21" s="3"/>
-      <c r="AY21" s="3"/>
-      <c r="AZ21" s="3"/>
-      <c r="BA21" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="BB21" s="10">
+      <c r="AU21" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AV21" s="2"/>
+      <c r="AW21" s="2"/>
+      <c r="AX21" s="2"/>
+      <c r="AY21" s="2"/>
+      <c r="AZ21" s="2"/>
+      <c r="BA21" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="BB21" s="8">
         <v>0</v>
       </c>
-      <c r="BC21" s="10">
+      <c r="BC21" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BD21" s="3"/>
-      <c r="BE21" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="BF21" s="10">
+      <c r="BD21" s="2"/>
+      <c r="BE21" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="BF21" s="8">
         <v>0</v>
       </c>
-      <c r="BG21" s="4"/>
+      <c r="BG21" s="3"/>
     </row>
     <row r="22" spans="1:59" ht="14.15" customHeight="1">
-      <c r="A22" s="19"/>
-      <c r="B22" s="11" t="s">
+      <c r="A22" s="25"/>
+      <c r="B22" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12" t="s">
+      <c r="C22" s="10"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12" t="s">
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="W22" s="12" t="s">
+      <c r="W22" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="12"/>
-      <c r="AA22" s="12"/>
-      <c r="AB22" s="12"/>
-      <c r="AC22" s="12"/>
-      <c r="AD22" s="12" t="s">
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10"/>
+      <c r="Z22" s="10"/>
+      <c r="AA22" s="10"/>
+      <c r="AB22" s="10"/>
+      <c r="AC22" s="10"/>
+      <c r="AD22" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="AE22" s="12"/>
-      <c r="AF22" s="12"/>
-      <c r="AG22" s="12"/>
-      <c r="AH22" s="12"/>
-      <c r="AI22" s="12"/>
-      <c r="AJ22" s="12"/>
-      <c r="AK22" s="12"/>
-      <c r="AL22" s="12"/>
-      <c r="AM22" s="12"/>
-      <c r="AN22" s="12"/>
-      <c r="AO22" s="12"/>
-      <c r="AP22" s="12"/>
-      <c r="AQ22" s="12"/>
-      <c r="AR22" s="12"/>
-      <c r="AS22" s="12"/>
-      <c r="AT22" s="12"/>
-      <c r="AU22" s="12"/>
-      <c r="AV22" s="12"/>
-      <c r="AW22" s="12"/>
-      <c r="AX22" s="12"/>
-      <c r="AY22" s="12"/>
-      <c r="AZ22" s="12"/>
-      <c r="BA22" s="12"/>
-      <c r="BB22" s="12"/>
-      <c r="BC22" s="12"/>
-      <c r="BD22" s="12"/>
-      <c r="BE22" s="12"/>
-      <c r="BF22" s="12"/>
-      <c r="BG22" s="13"/>
+      <c r="AE22" s="10"/>
+      <c r="AF22" s="10"/>
+      <c r="AG22" s="10"/>
+      <c r="AH22" s="10"/>
+      <c r="AI22" s="10"/>
+      <c r="AJ22" s="10"/>
+      <c r="AK22" s="10"/>
+      <c r="AL22" s="10"/>
+      <c r="AM22" s="10"/>
+      <c r="AN22" s="10"/>
+      <c r="AO22" s="10"/>
+      <c r="AP22" s="10"/>
+      <c r="AQ22" s="10"/>
+      <c r="AR22" s="10"/>
+      <c r="AS22" s="10"/>
+      <c r="AT22" s="10"/>
+      <c r="AU22" s="10"/>
+      <c r="AV22" s="10"/>
+      <c r="AW22" s="10"/>
+      <c r="AX22" s="10"/>
+      <c r="AY22" s="10"/>
+      <c r="AZ22" s="10"/>
+      <c r="BA22" s="10"/>
+      <c r="BB22" s="10"/>
+      <c r="BC22" s="10"/>
+      <c r="BD22" s="10"/>
+      <c r="BE22" s="10"/>
+      <c r="BF22" s="10"/>
+      <c r="BG22" s="11"/>
     </row>
     <row r="23" spans="1:59" ht="14.15" customHeight="1" thickBot="1">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <v>0.03</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="8">
         <v>0.02</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="7">
         <v>0.05</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="8">
         <v>0.02</v>
       </c>
-      <c r="F23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="G23" s="10">
+      <c r="F23" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="G23" s="8">
         <v>0.03</v>
       </c>
-      <c r="H23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="I23" s="10">
+      <c r="H23" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="I23" s="8">
         <v>0.08</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="8">
         <v>0.12</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="8">
         <v>0.1</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="8">
         <v>0.08</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M23" s="8">
         <v>0.19</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="8">
         <v>0.03</v>
       </c>
-      <c r="O23" s="9">
+      <c r="O23" s="7">
         <v>0.09</v>
       </c>
-      <c r="P23" s="10">
+      <c r="P23" s="8">
         <v>0.04</v>
       </c>
-      <c r="Q23" s="10">
+      <c r="Q23" s="8">
         <v>0</v>
       </c>
-      <c r="R23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="S23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="T23" s="10">
+      <c r="R23" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="S23" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="T23" s="8">
         <v>0</v>
       </c>
-      <c r="U23" s="10">
+      <c r="U23" s="8">
         <v>0</v>
       </c>
-      <c r="V23" s="10">
+      <c r="V23" s="8">
         <v>0.02</v>
       </c>
-      <c r="W23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="X23" s="10">
+      <c r="W23" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="X23" s="8">
         <v>0.02</v>
       </c>
-      <c r="Y23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="Z23" s="10">
+      <c r="Y23" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="Z23" s="8">
         <v>0.08</v>
       </c>
-      <c r="AA23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AB23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AC23" s="10">
+      <c r="AA23" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AB23" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AC23" s="8">
         <v>0.02</v>
       </c>
-      <c r="AD23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AE23" s="10">
+      <c r="AD23" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="AE23" s="8">
         <v>0</v>
       </c>
-      <c r="AF23" s="10">
+      <c r="AF23" s="8">
         <v>0.21</v>
       </c>
-      <c r="AG23" s="10">
+      <c r="AG23" s="8">
         <v>0.05</v>
       </c>
-      <c r="AH23" s="10">
+      <c r="AH23" s="8">
         <v>0.02</v>
       </c>
-      <c r="AI23" s="10">
+      <c r="AI23" s="8">
         <v>0.13</v>
       </c>
-      <c r="AJ23" s="10">
+      <c r="AJ23" s="8">
         <v>0.12</v>
       </c>
-      <c r="AK23" s="3"/>
-      <c r="AL23" s="10">
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="8">
         <v>0.09</v>
       </c>
-      <c r="AM23" s="10">
+      <c r="AM23" s="8">
         <v>0.21</v>
       </c>
-      <c r="AN23" s="10">
+      <c r="AN23" s="8">
         <v>0.05</v>
       </c>
-      <c r="AO23" s="10">
+      <c r="AO23" s="8">
         <v>0.19</v>
       </c>
-      <c r="AP23" s="3"/>
-      <c r="AQ23" s="3"/>
-      <c r="AR23" s="10">
+      <c r="AP23" s="2"/>
+      <c r="AQ23" s="2"/>
+      <c r="AR23" s="8">
         <v>0.11</v>
       </c>
-      <c r="AS23" s="10">
+      <c r="AS23" s="8">
         <v>0</v>
       </c>
-      <c r="AT23" s="10">
+      <c r="AT23" s="8">
         <v>0.02</v>
       </c>
-      <c r="AU23" s="10">
+      <c r="AU23" s="8">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AV23" s="10">
+      <c r="AV23" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AW23" s="3"/>
-      <c r="AX23" s="10">
+      <c r="AW23" s="2"/>
+      <c r="AX23" s="8">
         <v>0.12</v>
       </c>
-      <c r="AY23" s="10">
+      <c r="AY23" s="8">
         <v>0.16</v>
       </c>
-      <c r="AZ23" s="10">
+      <c r="AZ23" s="8">
         <v>0.04</v>
       </c>
-      <c r="BA23" s="10">
+      <c r="BA23" s="8">
         <v>0.03</v>
       </c>
-      <c r="BB23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="BC23" s="10">
+      <c r="BB23" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="BC23" s="8">
         <v>0.1</v>
       </c>
-      <c r="BD23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="BE23" s="10">
+      <c r="BD23" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="BE23" s="8">
         <v>0.06</v>
       </c>
-      <c r="BF23" s="3"/>
-      <c r="BG23" s="4"/>
+      <c r="BF23" s="2"/>
+      <c r="BG23" s="3"/>
     </row>
     <row r="24" spans="1:59" ht="14.15" customHeight="1" thickBot="1">
-      <c r="A24" s="20"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="26"/>
+      <c r="B24" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="H24" s="15" t="s">
+      <c r="H24" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="I24" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="J24" s="15" t="s">
+      <c r="J24" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="K24" s="15" t="s">
+      <c r="K24" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="L24" s="15" t="s">
+      <c r="L24" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="M24" s="15" t="s">
+      <c r="M24" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="N24" s="15" t="s">
+      <c r="N24" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="O24" s="14" t="s">
+      <c r="O24" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="P24" s="15" t="s">
+      <c r="P24" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="Q24" s="15" t="s">
+      <c r="Q24" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="R24" s="15" t="s">
+      <c r="R24" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="S24" s="15"/>
-      <c r="T24" s="15" t="s">
+      <c r="S24" s="13"/>
+      <c r="T24" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="U24" s="15" t="s">
+      <c r="U24" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="V24" s="15" t="s">
+      <c r="V24" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="W24" s="15" t="s">
+      <c r="W24" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="X24" s="15" t="s">
+      <c r="X24" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="Y24" s="15"/>
-      <c r="Z24" s="15" t="s">
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="AA24" s="15" t="s">
+      <c r="AA24" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="AB24" s="15" t="s">
+      <c r="AB24" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="AC24" s="15" t="s">
+      <c r="AC24" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="AD24" s="15" t="s">
+      <c r="AD24" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="AE24" s="15" t="s">
+      <c r="AE24" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="AF24" s="15" t="s">
+      <c r="AF24" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="AG24" s="15" t="s">
+      <c r="AG24" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="AH24" s="15"/>
-      <c r="AI24" s="15" t="s">
+      <c r="AH24" s="13"/>
+      <c r="AI24" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="AJ24" s="15" t="s">
+      <c r="AJ24" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="AK24" s="15"/>
-      <c r="AL24" s="15" t="s">
+      <c r="AK24" s="13"/>
+      <c r="AL24" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="AM24" s="15" t="s">
+      <c r="AM24" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="AN24" s="15" t="s">
+      <c r="AN24" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="AO24" s="15" t="s">
+      <c r="AO24" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="AP24" s="15"/>
-      <c r="AQ24" s="15"/>
-      <c r="AR24" s="15" t="s">
+      <c r="AP24" s="13"/>
+      <c r="AQ24" s="13"/>
+      <c r="AR24" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="AS24" s="15" t="s">
+      <c r="AS24" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="AT24" s="15" t="s">
+      <c r="AT24" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="AU24" s="15" t="s">
+      <c r="AU24" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="AV24" s="15" t="s">
+      <c r="AV24" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="AW24" s="15"/>
-      <c r="AX24" s="15"/>
-      <c r="AY24" s="15"/>
-      <c r="AZ24" s="15"/>
-      <c r="BA24" s="15"/>
-      <c r="BB24" s="15" t="s">
+      <c r="AW24" s="13"/>
+      <c r="AX24" s="13"/>
+      <c r="AY24" s="13"/>
+      <c r="AZ24" s="13"/>
+      <c r="BA24" s="13"/>
+      <c r="BB24" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="BC24" s="15" t="s">
+      <c r="BC24" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="BD24" s="15" t="s">
+      <c r="BD24" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="BE24" s="15" t="s">
+      <c r="BE24" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="BF24" s="15"/>
-      <c r="BG24" s="16"/>
+      <c r="BF24" s="13"/>
+      <c r="BG24" s="14"/>
     </row>
     <row r="26" spans="1:59" ht="13">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="17" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:59" ht="13">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="17" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="28" spans="1:59" ht="13">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="17" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="29" spans="1:59" ht="13">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="17" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="30" spans="1:59">
-      <c r="A30" s="17"/>
+      <c r="A30" s="15"/>
     </row>
     <row r="31" spans="1:59">
-      <c r="A31" s="18"/>
+      <c r="A31" s="16"/>
     </row>
     <row r="32" spans="1:59">
-      <c r="A32" s="18"/>
+      <c r="A32" s="16"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="18"/>
+      <c r="A33" s="16"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="18"/>
+      <c r="A34" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:O2"/>
     <mergeCell ref="P2:BG2"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A23:A24"/>
@@ -5471,6 +5471,11 @@
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:O2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
